--- a/web/files/港岛-香港仔及鸭脷洲-弦岸.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-弦岸.xlsx
@@ -841,7 +841,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3779,7 +3779,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3841,7 +3841,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4275,7 +4275,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4399,7 +4399,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4585,7 +4585,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -4833,7 +4833,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -4895,7 +4895,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5205,7 +5205,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5267,7 +5267,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -5825,7 +5825,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -5949,7 +5949,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -6259,7 +6259,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6445,7 +6445,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -6507,7 +6507,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -6569,7 +6569,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -6631,7 +6631,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -6693,7 +6693,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -6879,7 +6879,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7127,7 +7127,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -7189,7 +7189,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -7454,7 +7454,7 @@
           <t>D | 272呎 (1房)
 $734万
 $26,999/呎
-(24年-11月-28日)</t>
+(24年-11月-29日)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
@@ -7579,7 +7579,7 @@
           <t>B | 292呎 (1房)
 $773万
 $26,486/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="D8" s="23" t="inlineStr">
@@ -7595,7 +7595,7 @@
           <t>D | 272呎 (1房)
 $715万
 $26,276/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="F8" s="23" t="inlineStr">
@@ -7626,7 +7626,7 @@
           <t>B | 292呎 (1房)
 $698万
 $23,901/呎
-(26年-04月-14日)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="D9" s="23" t="inlineStr">
@@ -7642,7 +7642,7 @@
           <t>D | 272呎 (1房)
 $598万
 $21,982/呎
-(26年-03月-25日)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
@@ -7650,7 +7650,7 @@
           <t>E | 274呎 (1房)
 $598万
 $21,821/呎
-(26年-04月-15日)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
     </row>
@@ -7673,7 +7673,7 @@
           <t>B | 292呎 (1房)
 $658万
 $22,527/呎
-(26年-04月-15日)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -7689,7 +7689,7 @@
           <t>D | 272呎 (1房)
 $590万
 $21,691/呎
-(26年-04月-12日)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr">
@@ -7697,7 +7697,7 @@
           <t>E | 274呎 (1房)
 $581万
 $21,193/呎
-(26年-04月-15日)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
     </row>
@@ -7720,7 +7720,7 @@
           <t>B | 292呎 (1房)
 $650万
 $22,264/呎
-(26年-04月-20日)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -7728,7 +7728,7 @@
           <t>C | 206呎 (开放式)
 $484万
 $23,495/呎
-(26年-05月-03日)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="E11" s="21" t="inlineStr">
@@ -7736,7 +7736,7 @@
           <t>D | 272呎 (1房)
 $554万
 $20,364/呎
-(26年-02月-05日)</t>
+(26年-02月-06日)</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr">
@@ -7744,7 +7744,7 @@
           <t>E | 274呎 (1房)
 $563万
 $20,551/呎
-(26年-04月-19日)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
     </row>
@@ -7767,7 +7767,7 @@
           <t>B | 292呎 (1房)
 $614万
 $21,017/呎
-(26年-01月-25日)</t>
+(26年-01月-26日)</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -7775,7 +7775,7 @@
           <t>C | 206呎 (开放式)
 $479万
 $23,252/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr">
@@ -7783,7 +7783,7 @@
           <t>D | 272呎 (1房)
 $567万
 $20,846/呎
-(26年-02月-23日)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr">
@@ -7791,7 +7791,7 @@
           <t>E | 274呎 (1房)
 $576万
 $21,018/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -7814,7 +7814,7 @@
           <t>B | 292呎 (1房)
 $608万
 $20,808/呎
-(26年-02月-10日)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
@@ -7822,7 +7822,7 @@
           <t>C | 206呎 (开放式)
 $434万
 $21,073/呎
-(25年-08月-28日)</t>
+(25年-08月-29日)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr">
@@ -7830,7 +7830,7 @@
           <t>D | 272呎 (1房)
 $543万
 $19,963/呎
-(26年-01月-29日)</t>
+(26年-01月-30日)</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr">
@@ -7838,7 +7838,7 @@
           <t>E | 274呎 (1房)
 $552万
 $20,142/呎
-(26年-04月-13日)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
           <t>A | 316呎 (1房)
 $646万
 $20,446/呎
-(26年-03月-26日)</t>
+(26年-03月-27日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -7861,7 +7861,7 @@
           <t>B | 292呎 (1房)
 $632万
 $21,658/呎
-(26年-02月-15日)</t>
+(26年-02月-16日)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -7869,7 +7869,7 @@
           <t>C | 206呎 (开放式)
 $438万
 $21,238/呎
-(25年-07月-14日)</t>
+(25年-07月-15日)</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr">
@@ -7877,7 +7877,7 @@
           <t>D | 272呎 (1房)
 $538万
 $19,798/呎
-(26年-01月-14日)</t>
+(26年-01月-15日)</t>
         </is>
       </c>
       <c r="F14" s="21" t="inlineStr">
@@ -7885,7 +7885,7 @@
           <t>E | 274呎 (1房)
 $547万
 $19,974/呎
-(26年-04月-13日)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
     </row>
@@ -7900,7 +7900,7 @@
           <t>A | 316呎 (1房)
 $639万
 $20,225/呎
-(26年-04月-15日)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -7908,7 +7908,7 @@
           <t>B | 292呎 (1房)
 $598万
 $20,490/呎
-(26年-02月-01日)</t>
+(26年-02月-02日)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -7916,7 +7916,7 @@
           <t>C | 206呎 (开放式)
 $425万
 $20,636/呎
-(25年-07月-01日)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
@@ -7924,7 +7924,7 @@
           <t>D | 272呎 (1房)
 $532万
 $19,562/呎
-(25年-10月-21日)</t>
+(25年-10月-22日)</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr">
@@ -7932,7 +7932,7 @@
           <t>E | 274呎 (1房)
 $542万
 $19,777/呎
-(26年-04月-12日)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
     </row>
@@ -7947,7 +7947,7 @@
           <t>A | 316呎 (1房)
 $635万
 $20,108/呎
-(26年-03月-05日)</t>
+(26年-03月-06日)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -7955,7 +7955,7 @@
           <t>B | 292呎 (1房)
 $592万
 $20,291/呎
-(26年-01月-26日)</t>
+(26年-01月-27日)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -7963,7 +7963,7 @@
           <t>C | 206呎 (开放式)
 $421万
 $20,427/呎
-(25年-06月-09日)</t>
+(25年-06月-10日)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
@@ -7971,7 +7971,7 @@
           <t>D | 272呎 (1房)
 $529万
 $19,441/呎
-(25年-12月-23日)</t>
+(25年-12月-24日)</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr">
@@ -7979,7 +7979,7 @@
           <t>E | 274呎 (1房)
 $536万
 $19,577/呎
-(26年-04月-12日)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
     </row>
@@ -7994,7 +7994,7 @@
           <t>A | 316呎 (1房)
 $644万
 $20,364/呎
-(25年-03月-20日)</t>
+(25年-03月-21日)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -8002,7 +8002,7 @@
           <t>B | 292呎 (1房)
 $618万
 $21,182/呎
-(25年-06月-17日)</t>
+(25年-06月-18日)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -8010,7 +8010,7 @@
           <t>C | 206呎 (开放式)
 $403万
 $19,583/呎
-(24年-06月-02日)</t>
+(24年-06月-03日)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
@@ -8018,7 +8018,7 @@
           <t>D | 272呎 (1房)
 $541万
 $19,893/呎
-(25年-04月-29日)</t>
+(25年-04月-30日)</t>
         </is>
       </c>
       <c r="F17" s="21" t="inlineStr">
@@ -8026,7 +8026,7 @@
           <t>E | 274呎 (1房)
 $533万
 $19,460/呎
-(25年-08月-11日)</t>
+(25年-08月-12日)</t>
         </is>
       </c>
     </row>
@@ -8041,7 +8041,7 @@
           <t>A | 316呎 (1房)
 $627万
 $19,845/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -8049,7 +8049,7 @@
           <t>B | 292呎 (1房)
 $584万
 $20,014/呎
-(26年-01月-12日)</t>
+(26年-01月-13日)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -8057,7 +8057,7 @@
           <t>C | 205呎 (开放式)
 $406万
 $19,815/呎
-(24年-09月-16日)</t>
+(24年-09月-17日)</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr">
@@ -8065,7 +8065,7 @@
           <t>D | 272呎 (1房)
 $547万
 $20,103/呎
-(25年-06月-09日)</t>
+(25年-06月-10日)</t>
         </is>
       </c>
       <c r="F18" s="21" t="inlineStr">
@@ -8073,7 +8073,7 @@
           <t>E | 274呎 (1房)
 $537万
 $19,591/呎
-(25年-08月-11日)</t>
+(25年-08月-12日)</t>
         </is>
       </c>
     </row>
@@ -8088,7 +8088,7 @@
           <t>A | 316呎 (1房)
 $634万
 $20,070/呎
-(25年-06月-12日)</t>
+(25年-06月-13日)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -8096,7 +8096,7 @@
           <t>B | 292呎 (1房)
 $581万
 $19,911/呎
-(26年-01月-06日)</t>
+(26年-01月-07日)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -8104,7 +8104,7 @@
           <t>C | 205呎 (开放式)
 $396万
 $19,312/呎
-(24年-09月-04日)</t>
+(24年-09月-05日)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
@@ -8112,7 +8112,7 @@
           <t>D | 272呎 (1房)
 $533万
 $19,599/呎
-(25年-06月-04日)</t>
+(25年-06月-05日)</t>
         </is>
       </c>
       <c r="F19" s="21" t="inlineStr">
@@ -8120,7 +8120,7 @@
           <t>E | 274呎 (1房)
 $525万
 $19,172/呎
-(25年-08月-07日)</t>
+(25年-08月-08日)</t>
         </is>
       </c>
     </row>
@@ -8143,7 +8143,7 @@
           <t>B | 292呎 (1房)
 $576万
 $19,733/呎
-(25年-10月-27日)</t>
+(25年-10月-28日)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -8151,7 +8151,7 @@
           <t>C | 205呎 (开放式)
 $399万
 $19,454/呎
-(24年-11月-18日)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
@@ -8159,7 +8159,7 @@
           <t>D | 272呎 (1房)
 $539万
 $19,824/呎
-(25年-07月-07日)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="F20" s="21" t="inlineStr">
@@ -8167,7 +8167,7 @@
           <t>E | 274呎 (1房)
 $529万
 $19,314/呎
-(25年-08月-21日)</t>
+(25年-08月-22日)</t>
         </is>
       </c>
     </row>
@@ -8182,7 +8182,7 @@
           <t>A | 316呎 (1房)
 $626万
 $19,804/呎
-(25年-07月-01日)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -8190,7 +8190,7 @@
           <t>B | 292呎 (1房)
 $599万
 $20,527/呎
-(25年-08月-06日)</t>
+(25年-08月-07日)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -8198,7 +8198,7 @@
           <t>C | 205呎 (开放式)
 $387万
 $18,893/呎
-(24年-06月-02日)</t>
+(24年-06月-03日)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -8206,7 +8206,7 @@
           <t>D | 272呎 (1房)
 $526万
 $19,338/呎
-(25年-04月-02日)</t>
+(25年-04月-03日)</t>
         </is>
       </c>
       <c r="F21" s="21" t="inlineStr">
@@ -8214,7 +8214,7 @@
           <t>E | 274呎 (1房)
 $516万
 $18,832/呎
-(25年-07月-17日)</t>
+(25年-07月-18日)</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8237,7 @@
           <t>B | 292呎 (1房)
 $571万
 $19,568/呎
-(26年-01月-06日)</t>
+(26年-01月-07日)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -8245,7 +8245,7 @@
           <t>C | 205呎 (开放式)
 $394万
 $19,210/呎
-(25年-03月-12日)</t>
+(25年-03月-13日)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -8253,7 +8253,7 @@
           <t>D | 272呎 (1房)
 $535万
 $19,654/呎
-(25年-07月-14日)</t>
+(25年-07月-15日)</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr">
@@ -8261,7 +8261,7 @@
           <t>E | 274呎 (1房)
 $525万
 $19,146/呎
-(25年-07月-14日)</t>
+(25年-07月-15日)</t>
         </is>
       </c>
     </row>
@@ -8276,7 +8276,7 @@
           <t>A | 316呎 (1房)
 $616万
 $19,484/呎
-(25年-08月-03日)</t>
+(25年-08月-04日)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -8284,7 +8284,7 @@
           <t>B | 292呎 (1房)
 $592万
 $20,277/呎
-(25年-08月-13日)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -8292,7 +8292,7 @@
           <t>C | 205呎 (开放式)
 $379万
 $18,502/呎
-(24年-05月-15日)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
@@ -8300,7 +8300,7 @@
           <t>D | 272呎 (1房)
 $517万
 $19,022/呎
-(25年-03月-13日)</t>
+(25年-03月-14日)</t>
         </is>
       </c>
       <c r="F23" s="21" t="inlineStr">
@@ -8308,7 +8308,7 @@
           <t>E | 274呎 (1房)
 $508万
 $18,522/呎
-(25年-07月-14日)</t>
+(25年-07月-15日)</t>
         </is>
       </c>
     </row>
@@ -8323,7 +8323,7 @@
           <t>A | 316呎 (1房)
 $617万
 $19,519/呎
-(25年-08月-28日)</t>
+(25年-08月-29日)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
@@ -8331,7 +8331,7 @@
           <t>B | 292呎 (1房)
 $561万
 $19,199/呎
-(26年-01月-29日)</t>
+(26年-01月-30日)</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -8339,7 +8339,7 @@
           <t>C | 205呎 (开放式)
 $383万
 $18,673/呎
-(24年-08月-22日)</t>
+(24年-08月-23日)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
@@ -8347,7 +8347,7 @@
           <t>D | 272呎 (1房)
 $509万
 $18,721/呎
-(24年-11月-10日)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="F24" s="21" t="inlineStr">
@@ -8355,7 +8355,7 @@
           <t>E | 274呎 (1房)
 $499万
 $18,223/呎
-(25年-06月-04日)</t>
+(25年-06月-05日)</t>
         </is>
       </c>
     </row>
@@ -8378,7 +8378,7 @@
           <t>B | 292呎 (1房)
 $554万
 $18,979/呎
-(26年-01月-29日)</t>
+(26年-01月-30日)</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -8386,7 +8386,7 @@
           <t>C | 205呎 (开放式)
 $369万
 $17,990/呎
-(24年-06月-02日)</t>
+(24年-06月-03日)</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
@@ -8394,7 +8394,7 @@
           <t>D | 235呎 (1房)
 $630万
 $26,809/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="F25" s="21" t="inlineStr">
@@ -8402,7 +8402,7 @@
           <t>E | 237呎 (1房)
 $530万
 $22,363/呎
-(25年-10月-19日)</t>
+(25年-10月-20日)</t>
         </is>
       </c>
     </row>

--- a/web/files/港岛-香港仔及鸭脷洲-弦岸.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-弦岸.xlsx
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>7219000</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>35215</v>
+        <v>35044</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>5504488</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>26851</v>
+        <v>26721</v>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
@@ -7678,9 +7678,9 @@
       </c>
       <c r="D10" s="23" t="inlineStr">
         <is>
-          <t>C | 205呎 (开放式)
+          <t>C | 206呎 (开放式)
 $722万
-$35,215/呎
+$35,044/呎
 (在售)</t>
         </is>
       </c>
